--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79833</v>
+        <v>79834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79862</v>
+        <v>79863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79833</v>
+        <v>79834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79834</v>
+        <v>79835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79863</v>
+        <v>79864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79834</v>
+        <v>79835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2840,7 +2840,7 @@
         <v>131106801</v>
       </c>
       <c r="B20" t="n">
-        <v>57300</v>
+        <v>57302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131106800</v>
       </c>
       <c r="B22" t="n">
-        <v>57300</v>
+        <v>57302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131106669</v>
       </c>
       <c r="B25" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2840,7 +2840,7 @@
         <v>131106801</v>
       </c>
       <c r="B20" t="n">
-        <v>57302</v>
+        <v>57303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131106800</v>
       </c>
       <c r="B22" t="n">
-        <v>57302</v>
+        <v>57303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131106669</v>
       </c>
       <c r="B25" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2840,7 +2840,7 @@
         <v>131106801</v>
       </c>
       <c r="B20" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131106800</v>
       </c>
       <c r="B22" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2840,7 +2840,7 @@
         <v>131106801</v>
       </c>
       <c r="B20" t="n">
-        <v>57304</v>
+        <v>57307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131106800</v>
       </c>
       <c r="B22" t="n">
-        <v>57304</v>
+        <v>57307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131106669</v>
       </c>
       <c r="B25" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -2840,7 +2840,7 @@
         <v>131106801</v>
       </c>
       <c r="B20" t="n">
-        <v>57307</v>
+        <v>57308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>131106774</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131106800</v>
       </c>
       <c r="B22" t="n">
-        <v>57307</v>
+        <v>57308</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131106775</v>
       </c>
       <c r="B23" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>131106670</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131106669</v>
       </c>
       <c r="B25" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56051946</v>
+        <v>118719302</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600364.1107609756</v>
+        <v>600342</v>
       </c>
       <c r="R2" t="n">
-        <v>6972498.23584515</v>
+        <v>6972364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>gles, 160-årig tallskog med brandspår</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -786,33 +767,28 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga</t>
+          <t>1 substratenheter # mycket gammal lump efter gammal talltopp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117863966</v>
+        <v>56051946</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,34 +796,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600369</v>
+        <v>600364</v>
       </c>
       <c r="R3" t="n">
-        <v>6972469</v>
+        <v>6972498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2015-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2015-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,31 +870,39 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117863965</v>
+        <v>118719301</v>
       </c>
       <c r="B4" t="n">
-        <v>90523</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,34 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600277</v>
+        <v>600326</v>
       </c>
       <c r="R4" t="n">
-        <v>6972625</v>
+        <v>6972303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,53 +980,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gles, 160-årig tallskog med brandspår på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # hård gammal tallåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118719301</v>
+        <v>118719305</v>
       </c>
       <c r="B5" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600326</v>
+        <v>600283</v>
       </c>
       <c r="R5" t="n">
-        <v>6972303</v>
+        <v>6972642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1093,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gles, 160-årig tallskog med brandspår på blockig morän</t>
+          <t>gles, 160-årig tallskog med brandspår</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # hård gammal tallåga</t>
+          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,37 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118719305</v>
+        <v>118719303</v>
       </c>
       <c r="B6" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600283</v>
+        <v>600346</v>
       </c>
       <c r="R6" t="n">
-        <v>6972642</v>
+        <v>6972577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1203,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
+          <t>160-årig tallskog med lövinslag på blockig morän</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1220,7 +1211,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
+          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1238,50 +1229,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118719302</v>
+        <v>117863965</v>
       </c>
       <c r="B7" t="n">
-        <v>90758</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600342</v>
+        <v>600277</v>
       </c>
       <c r="R7" t="n">
-        <v>6972364</v>
+        <v>6972625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,12 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,44 +1310,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # mycket gammal lump efter gammal talltopp</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118719306</v>
+        <v>123301015</v>
       </c>
       <c r="B8" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,34 +1337,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600287</v>
+        <v>600278</v>
       </c>
       <c r="R8" t="n">
-        <v>6972642</v>
+        <v>6972629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,14 +1389,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,79 +1422,65 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118719303</v>
+        <v>123301018</v>
       </c>
       <c r="B9" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600346</v>
+        <v>600361</v>
       </c>
       <c r="R9" t="n">
-        <v>6972577</v>
+        <v>6972470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,14 +1505,34 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förekommer i hela beståndet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,44 +1543,30 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>160-årig tallskog med lövinslag på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Simon Selberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123301025</v>
+        <v>123301026</v>
       </c>
       <c r="B10" t="n">
-        <v>79377</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600360</v>
+        <v>600366</v>
       </c>
       <c r="R10" t="n">
-        <v>6972357</v>
+        <v>6972325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1628,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1663,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1668,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1704,15 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123301026</v>
+        <v>123435054</v>
       </c>
       <c r="B11" t="n">
-        <v>78172</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600366</v>
+        <v>600318</v>
       </c>
       <c r="R11" t="n">
-        <v>6972325</v>
+        <v>6972649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1744,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1784,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,6 +1775,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1814,7 +1794,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Douglas Skarp, Simon Selberg, Måns Svensson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1825,15 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123301015</v>
+        <v>131106803</v>
       </c>
       <c r="B12" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,34 +1816,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600278</v>
+        <v>600279</v>
       </c>
       <c r="R12" t="n">
-        <v>6972629</v>
+        <v>6972994</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,27 +1879,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1919,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1946,54 +1930,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123301017</v>
+        <v>123301021</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600330</v>
+        <v>600343</v>
       </c>
       <c r="R13" t="n">
-        <v>6972678</v>
+        <v>6972449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +1995,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2030,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En tupp</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2035,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2076,15 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123301019</v>
+        <v>131106775</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,34 +2057,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600370</v>
+        <v>600380</v>
       </c>
       <c r="R14" t="n">
-        <v>6972469</v>
+        <v>6972329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,27 +2120,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>2025_0401</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,16 +2151,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2196,7 +2160,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
+          <t>David Isaksson, Karin Halldin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2207,37 +2171,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123301014</v>
+        <v>123435055</v>
       </c>
       <c r="B15" t="n">
-        <v>79377</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2247,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600283</v>
+        <v>600350</v>
       </c>
       <c r="R15" t="n">
-        <v>6972652</v>
+        <v>6972407</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2236,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>864</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2287,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,6 +2267,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2328,15 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123301021</v>
+        <v>117863966</v>
       </c>
       <c r="B16" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,34 +2308,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600343</v>
+        <v>600369</v>
       </c>
       <c r="R16" t="n">
-        <v>6972449</v>
+        <v>6972469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,29 +2360,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:48</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:48</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,31 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123301018</v>
+        <v>123301019</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,21 +2405,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600361</v>
+        <v>600370</v>
       </c>
       <c r="R17" t="n">
-        <v>6972470</v>
+        <v>6972469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,7 +2459,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>867</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2529,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2539,12 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Förekommer i hela beståndet</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,6 +2490,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2564,7 +2509,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2575,50 +2520,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123435054</v>
+        <v>123301017</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600318</v>
+        <v>600330</v>
       </c>
       <c r="R18" t="n">
-        <v>6972649</v>
+        <v>6972678</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,7 +2589,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>869</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2655,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2665,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,16 +2625,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2695,7 +2634,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2706,15 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123435055</v>
+        <v>131106669</v>
       </c>
       <c r="B19" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,34 +2656,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600350</v>
+        <v>600375</v>
       </c>
       <c r="R19" t="n">
-        <v>6972407</v>
+        <v>6972262</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,27 +2714,27 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>2025_0507</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,16 +2745,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2826,7 +2754,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Douglas Skarp, Måns Svensson</t>
+          <t>Karin Halldin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2837,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106801</v>
+        <v>131106800</v>
       </c>
       <c r="B20" t="n">
-        <v>57308</v>
+        <v>57369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2876,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600200</v>
+        <v>600203</v>
       </c>
       <c r="R20" t="n">
-        <v>6973062</v>
+        <v>6973054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2834,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0375</t>
+          <t>2025_0376</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2916,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2962,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106774</v>
+        <v>131106801</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>57369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2973,21 +2901,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>102961</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2995,21 +2923,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600324</v>
+        <v>600200</v>
       </c>
       <c r="R21" t="n">
-        <v>6972295</v>
+        <v>6973062</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,27 +2959,32 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0402</t>
+          <t>2025_0375</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>par i häckbiotop</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3076,7 +3004,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3087,10 +3015,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131106800</v>
+        <v>118719306</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
+        <v>79917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,38 +3026,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102961</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600203</v>
+        <v>600287</v>
       </c>
       <c r="R22" t="n">
-        <v>6973054</v>
+        <v>6972642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,34 +3078,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2025_0376</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>par i häckbiotop</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3192,30 +3096,39 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>gles, 160-årig tallskog med brandspår</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131106775</v>
+        <v>123301014</v>
       </c>
       <c r="B23" t="n">
-        <v>79873</v>
+        <v>79917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,43 +3136,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600380</v>
+        <v>600283</v>
       </c>
       <c r="R23" t="n">
-        <v>6972329</v>
+        <v>6972652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3286,27 +3190,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2025_0401</t>
+          <t>872</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,7 +3230,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Isaksson, Karin Halldin</t>
+          <t>Måns Svensson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3337,10 +3241,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131106670</v>
+        <v>123301025</v>
       </c>
       <c r="B24" t="n">
-        <v>79844</v>
+        <v>79917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,26 +3269,17 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600304</v>
+        <v>600360</v>
       </c>
       <c r="R24" t="n">
-        <v>6972313</v>
+        <v>6972357</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3411,27 +3306,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2025_0506</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3451,7 +3346,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3462,37 +3357,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106669</v>
+        <v>131106670</v>
       </c>
       <c r="B25" t="n">
-        <v>57080</v>
+        <v>79917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3501,10 +3401,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600375</v>
+        <v>600304</v>
       </c>
       <c r="R25" t="n">
-        <v>6972262</v>
+        <v>6972313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3531,7 +3431,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2025_0507</t>
+          <t>2025_0506</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3541,7 +3441,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3551,7 +3451,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,6 +3475,131 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131106774</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nordansjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600324</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6972295</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2025_0402</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,48 +1009,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118719305</v>
+        <v>135342343</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600283</v>
+        <v>600216</v>
       </c>
       <c r="R5" t="n">
-        <v>6972642</v>
+        <v>6972924</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,12 +1077,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,61 +1103,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118719303</v>
+        <v>118719305</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600346</v>
+        <v>600283</v>
       </c>
       <c r="R6" t="n">
-        <v>6972577</v>
+        <v>6972642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>160-årig tallskog med lövinslag på blockig morän</t>
+          <t>gles, 160-årig tallskog med brandspår</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
+          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117863965</v>
+        <v>118719303</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600277</v>
+        <v>600346</v>
       </c>
       <c r="R7" t="n">
-        <v>6972625</v>
+        <v>6972577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,23 +1310,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>160-årig tallskog med lövinslag på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301015</v>
+        <v>117863965</v>
       </c>
       <c r="B8" t="n">
         <v>91930</v>
@@ -1357,14 +1370,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600278</v>
+        <v>600277</v>
       </c>
       <c r="R8" t="n">
-        <v>6972629</v>
+        <v>6972625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,29 +1402,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:09</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:09</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,48 +1424,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123301018</v>
+        <v>123301015</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600361</v>
+        <v>600278</v>
       </c>
       <c r="R9" t="n">
-        <v>6972470</v>
+        <v>6972629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1501,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1517,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,12 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förekommer i hela beståndet</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,7 +1541,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1563,32 +1552,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123301026</v>
+        <v>123301018</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600366</v>
+        <v>600361</v>
       </c>
       <c r="R10" t="n">
-        <v>6972325</v>
+        <v>6972470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1617,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1638,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1637,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förekommer i hela beståndet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1662,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1679,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123435054</v>
+        <v>123301026</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600318</v>
+        <v>600366</v>
       </c>
       <c r="R11" t="n">
-        <v>6972649</v>
+        <v>6972325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1738,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1754,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1764,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,16 +1769,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1794,7 +1778,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1805,7 +1789,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106803</v>
+        <v>123435054</v>
       </c>
       <c r="B12" t="n">
         <v>79084</v>
@@ -1833,26 +1817,17 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600279</v>
+        <v>600318</v>
       </c>
       <c r="R12" t="n">
-        <v>6972994</v>
+        <v>6972649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,27 +1854,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0373</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,6 +1885,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1919,7 +1904,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1930,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123301021</v>
+        <v>131106803</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1926,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600343</v>
+        <v>600279</v>
       </c>
       <c r="R13" t="n">
-        <v>6972449</v>
+        <v>6972994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,27 +1989,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,7 +2029,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2046,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106775</v>
+        <v>135342344</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>79130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,46 +2051,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600380</v>
+        <v>600280</v>
       </c>
       <c r="R14" t="n">
-        <v>6972329</v>
+        <v>6973063</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,29 +2106,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2025_0401</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,64 +2138,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson, Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123435055</v>
+        <v>135342345</v>
       </c>
       <c r="B15" t="n">
-        <v>80336</v>
+        <v>79130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600350</v>
+        <v>600215</v>
       </c>
       <c r="R15" t="n">
-        <v>6972407</v>
+        <v>6972928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2234,29 +2216,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,40 +2244,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117863966</v>
+        <v>123301021</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,34 +2271,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600369</v>
+        <v>600343</v>
       </c>
       <c r="R16" t="n">
-        <v>6972469</v>
+        <v>6972449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,14 +2323,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,22 +2360,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123301019</v>
+        <v>131106775</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,34 +2387,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600370</v>
+        <v>600380</v>
       </c>
       <c r="R17" t="n">
-        <v>6972469</v>
+        <v>6972329</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,27 +2450,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>2025_0401</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,16 +2481,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2509,7 +2490,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
+          <t>David Isaksson, Karin Halldin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2520,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123301017</v>
+        <v>123435055</v>
       </c>
       <c r="B18" t="n">
-        <v>57141</v>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,38 +2512,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600330</v>
+        <v>600350</v>
       </c>
       <c r="R18" t="n">
-        <v>6972678</v>
+        <v>6972407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2566,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>864</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2599,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2586,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En tupp</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,6 +2597,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2634,7 +2616,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Måns Svensson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2645,49 +2627,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131106669</v>
+        <v>117863966</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600375</v>
+        <v>600369</v>
       </c>
       <c r="R19" t="n">
-        <v>6972262</v>
+        <v>6972469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,29 +2690,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2025_0507</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,26 +2712,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106800</v>
+        <v>123301019</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,38 +2735,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102961</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600203</v>
+        <v>600370</v>
       </c>
       <c r="R20" t="n">
-        <v>6973054</v>
+        <v>6972469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,32 +2789,27 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0376</t>
+          <t>867</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>par i häckbiotop</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,6 +2820,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2879,7 +2839,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2890,27 +2850,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106801</v>
+        <v>123301017</v>
       </c>
       <c r="B21" t="n">
-        <v>57369</v>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102961</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2920,19 +2880,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600200</v>
+        <v>600330</v>
       </c>
       <c r="R21" t="n">
-        <v>6973062</v>
+        <v>6972678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2959,32 +2919,32 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0375</t>
+          <t>869</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>par i häckbiotop</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,7 +2964,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3015,45 +2975,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118719306</v>
+        <v>131106669</v>
       </c>
       <c r="B22" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600287</v>
+        <v>600375</v>
       </c>
       <c r="R22" t="n">
-        <v>6972642</v>
+        <v>6972262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3078,14 +3042,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2025_0507</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,39 +3075,30 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123301014</v>
+        <v>131106800</v>
       </c>
       <c r="B23" t="n">
-        <v>79917</v>
+        <v>57369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,34 +3106,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600283</v>
+        <v>600203</v>
       </c>
       <c r="R23" t="n">
-        <v>6972652</v>
+        <v>6973054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3190,27 +3164,32 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2025_0376</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>par i häckbiotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3230,7 +3209,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3241,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123301025</v>
+        <v>131106801</v>
       </c>
       <c r="B24" t="n">
-        <v>79917</v>
+        <v>57369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,34 +3231,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>102961</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600360</v>
+        <v>600200</v>
       </c>
       <c r="R24" t="n">
-        <v>6972357</v>
+        <v>6973062</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3306,27 +3289,32 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>2025_0375</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>par i häckbiotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,7 +3334,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3357,7 +3345,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106670</v>
+        <v>118719306</v>
       </c>
       <c r="B25" t="n">
         <v>79917</v>
@@ -3385,26 +3373,17 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600304</v>
+        <v>600287</v>
       </c>
       <c r="R25" t="n">
-        <v>6972313</v>
+        <v>6972642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3429,29 +3408,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2025_0506</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,27 +3426,36 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>gles, 160-årig tallskog med brandspår</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131106774</v>
+        <v>123301014</v>
       </c>
       <c r="B26" t="n">
         <v>79917</v>
@@ -3510,26 +3483,17 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600324</v>
+        <v>600283</v>
       </c>
       <c r="R26" t="n">
-        <v>6972295</v>
+        <v>6972652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3556,27 +3520,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0402</t>
+          <t>872</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3596,10 +3560,376 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
+          <t>Måns Svensson, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123301025</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600360</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6972357</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131106670</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nordansjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600304</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6972313</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2025_0506</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131106774</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nordansjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600324</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6972295</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2025_0402</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56051946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342343</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719305</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863965</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301018</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123435054</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106803</t>
         </is>
       </c>
     </row>
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342344</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2257,6 +2327,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342345</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2373,6 +2448,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2498,6 +2578,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106775</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2624,6 +2709,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123435055</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2721,6 +2811,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863966</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2972,6 +3072,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3092,6 +3197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106669</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3217,6 +3327,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106800</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3342,6 +3457,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106801</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3452,6 +3572,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719306</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3568,6 +3693,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301014</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3684,6 +3814,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3809,6 +3944,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106670</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3934,8 +4074,43 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106774</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>135342343</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>135342344</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>135342345</v>
       </c>
       <c r="B15" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>135342343</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>135342344</v>
       </c>
       <c r="B14" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>135342345</v>
       </c>
       <c r="B15" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 26089-2025 artfynd.xlsx
+++ b/artfynd/A 26089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,48 +1029,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118719305</v>
+        <v>135342343</v>
       </c>
       <c r="B5" t="n">
-        <v>92083</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600283</v>
+        <v>600216</v>
       </c>
       <c r="R5" t="n">
-        <v>6972642</v>
+        <v>6972924</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,12 +1097,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,66 +1123,53 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118719305</t>
+          <t>https://artportalen.se/Sighting/135342343</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118719303</v>
+        <v>118719305</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600346</v>
+        <v>600283</v>
       </c>
       <c r="R6" t="n">
-        <v>6972577</v>
+        <v>6972642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>160-årig tallskog med lövinslag på blockig morän</t>
+          <t>gles, 160-årig tallskog med brandspår</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
+          <t>1 substratenheter # gammal talltopp som lämnas vid avverkning på 1800-talet</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,16 +1253,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118719303</t>
+          <t>https://artportalen.se/Sighting/118719305</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117863965</v>
+        <v>118719303</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,34 +1270,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600277</v>
+        <v>600346</v>
       </c>
       <c r="R7" t="n">
-        <v>6972625</v>
+        <v>6972577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,28 +1340,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>160-årig tallskog med lövinslag på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # mycket gammalt vindfälle efter gammal tall</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117863965</t>
+          <t>https://artportalen.se/Sighting/118719303</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123301015</v>
+        <v>117863965</v>
       </c>
       <c r="B8" t="n">
         <v>91930</v>
@@ -1392,14 +1405,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600278</v>
+        <v>600277</v>
       </c>
       <c r="R8" t="n">
-        <v>6972629</v>
+        <v>6972625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,29 +1437,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:09</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:09</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,53 +1459,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301015</t>
+          <t>https://artportalen.se/Sighting/117863965</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123301018</v>
+        <v>123301015</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600361</v>
+        <v>600278</v>
       </c>
       <c r="R9" t="n">
-        <v>6972470</v>
+        <v>6972629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1541,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1557,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,12 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förekommer i hela beståndet</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1602,38 +1591,38 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301018</t>
+          <t>https://artportalen.se/Sighting/123301015</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123301026</v>
+        <v>123301018</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600366</v>
+        <v>600361</v>
       </c>
       <c r="R10" t="n">
-        <v>6972325</v>
+        <v>6972470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1662,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1683,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1682,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Förekommer i hela beståndet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1707,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1723,16 +1717,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301026</t>
+          <t>https://artportalen.se/Sighting/123301018</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123435054</v>
+        <v>123301026</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,21 +1734,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1764,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600318</v>
+        <v>600366</v>
       </c>
       <c r="R11" t="n">
-        <v>6972649</v>
+        <v>6972325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1788,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1804,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,16 +1819,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Gammal brandstubbe</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1844,7 +1828,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1854,13 +1838,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123435054</t>
+          <t>https://artportalen.se/Sighting/123301026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106803</v>
+        <v>123435054</v>
       </c>
       <c r="B12" t="n">
         <v>79084</v>
@@ -1888,26 +1872,17 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600279</v>
+        <v>600318</v>
       </c>
       <c r="R12" t="n">
-        <v>6972994</v>
+        <v>6972649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,27 +1909,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0373</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,6 +1940,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Gammal brandstubbe</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1974,7 +1959,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1984,16 +1969,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106803</t>
+          <t>https://artportalen.se/Sighting/123435054</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123301021</v>
+        <v>131106803</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,34 +1986,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600343</v>
+        <v>600279</v>
       </c>
       <c r="R13" t="n">
-        <v>6972449</v>
+        <v>6972994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,27 +2049,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,7 +2089,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2105,16 +2099,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301021</t>
+          <t>https://artportalen.se/Sighting/131106803</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131106775</v>
+        <v>135342344</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,46 +2116,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600380</v>
+        <v>600280</v>
       </c>
       <c r="R14" t="n">
-        <v>6972329</v>
+        <v>6973063</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,29 +2171,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2025_0401</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,69 +2203,68 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Isaksson, Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106775</t>
+          <t>https://artportalen.se/Sighting/135342344</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123435055</v>
+        <v>135342345</v>
       </c>
       <c r="B15" t="n">
-        <v>80336</v>
+        <v>79198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600350</v>
+        <v>600215</v>
       </c>
       <c r="R15" t="n">
-        <v>6972407</v>
+        <v>6972928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2304,29 +2286,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,45 +2314,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123435055</t>
+          <t>https://artportalen.se/Sighting/135342345</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117863966</v>
+        <v>123301021</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,34 +2346,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600369</v>
+        <v>600343</v>
       </c>
       <c r="R16" t="n">
-        <v>6972469</v>
+        <v>6972449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2435,14 +2398,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,27 +2435,31 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117863966</t>
+          <t>https://artportalen.se/Sighting/123301021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123301019</v>
+        <v>131106775</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,34 +2467,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600370</v>
+        <v>600380</v>
       </c>
       <c r="R17" t="n">
-        <v>6972469</v>
+        <v>6972329</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,27 +2530,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>2025_0401</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,16 +2561,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2589,7 +2570,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
+          <t>David Isaksson, Karin Halldin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2599,16 +2580,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301019</t>
+          <t>https://artportalen.se/Sighting/131106775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123301017</v>
+        <v>123435055</v>
       </c>
       <c r="B18" t="n">
-        <v>57141</v>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,38 +2597,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600330</v>
+        <v>600350</v>
       </c>
       <c r="R18" t="n">
-        <v>6972678</v>
+        <v>6972407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,7 +2651,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>864</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2684,7 +2661,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2694,12 +2671,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En tupp</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,6 +2682,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2719,7 +2701,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Simon Selberg</t>
+          <t>Måns Svensson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2729,55 +2711,51 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301017</t>
+          <t>https://artportalen.se/Sighting/123435055</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131106669</v>
+        <v>117863966</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600375</v>
+        <v>600369</v>
       </c>
       <c r="R19" t="n">
-        <v>6972262</v>
+        <v>6972469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2802,29 +2780,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2025_0507</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,31 +2802,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106669</t>
+          <t>https://artportalen.se/Sighting/117863966</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131106800</v>
+        <v>123301019</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,38 +2830,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102961</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600203</v>
+        <v>600370</v>
       </c>
       <c r="R20" t="n">
-        <v>6973054</v>
+        <v>6972469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2929,32 +2884,27 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2025_0376</t>
+          <t>867</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>par i häckbiotop</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,6 +2915,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2974,7 +2934,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Måns Svensson, Douglas Skarp, Simon Selberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2984,33 +2944,33 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106800</t>
+          <t>https://artportalen.se/Sighting/123301019</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131106801</v>
+        <v>123301017</v>
       </c>
       <c r="B21" t="n">
-        <v>57369</v>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102961</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3020,19 +2980,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600200</v>
+        <v>600330</v>
       </c>
       <c r="R21" t="n">
-        <v>6973062</v>
+        <v>6972678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3059,32 +3019,32 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2025_0375</t>
+          <t>869</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>par i häckbiotop</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3104,7 +3064,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Forsberg</t>
+          <t>Simon Selberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3114,51 +3074,55 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106801</t>
+          <t>https://artportalen.se/Sighting/123301017</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118719306</v>
+        <v>131106669</v>
       </c>
       <c r="B22" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nordansjöns östra sida, Mpd</t>
+          <t>Nordansjö, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600287</v>
+        <v>600375</v>
       </c>
       <c r="R22" t="n">
-        <v>6972642</v>
+        <v>6972262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3183,14 +3147,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2025_0507</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,44 +3180,35 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>gles, 160-årig tallskog med brandspår</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118719306</t>
+          <t>https://artportalen.se/Sighting/131106669</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123301014</v>
+        <v>131106800</v>
       </c>
       <c r="B23" t="n">
-        <v>79917</v>
+        <v>57369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,34 +3216,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600283</v>
+        <v>600203</v>
       </c>
       <c r="R23" t="n">
-        <v>6972652</v>
+        <v>6973054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3300,27 +3274,32 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2025_0376</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>par i häckbiotop</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3340,7 +3319,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Måns Svensson, Douglas Skarp</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3350,16 +3329,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301014</t>
+          <t>https://artportalen.se/Sighting/131106800</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123301025</v>
+        <v>131106801</v>
       </c>
       <c r="B24" t="n">
-        <v>79917</v>
+        <v>57369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3367,34 +3346,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>102961</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600360</v>
+        <v>600200</v>
       </c>
       <c r="R24" t="n">
-        <v>6972357</v>
+        <v>6973062</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3421,27 +3404,32 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>2025_0375</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>par i häckbiotop</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3461,7 +3449,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+          <t>Anders Forsberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3471,13 +3459,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123301025</t>
+          <t>https://artportalen.se/Sighting/131106801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131106670</v>
+        <v>118719306</v>
       </c>
       <c r="B25" t="n">
         <v>79917</v>
@@ -3505,26 +3493,17 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjöns östra sida, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600304</v>
+        <v>600287</v>
       </c>
       <c r="R25" t="n">
-        <v>6972313</v>
+        <v>6972642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3549,29 +3528,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2025_0506</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3582,32 +3546,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>gles, 160-årig tallskog med brandspår</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallhögstubbe, på hård ytved</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Halldin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106670</t>
+          <t>https://artportalen.se/Sighting/118719306</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131106774</v>
+        <v>123301014</v>
       </c>
       <c r="B26" t="n">
         <v>79917</v>
@@ -3635,26 +3608,17 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nordansjö, Mpd</t>
+          <t>Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600324</v>
+        <v>600283</v>
       </c>
       <c r="R26" t="n">
-        <v>6972295</v>
+        <v>6972652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3681,27 +3645,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025_0402</t>
+          <t>872</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3721,15 +3685,396 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
+          <t>Måns Svensson, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301014</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123301025</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600360</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6972357</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Simon Selberg, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131106670</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nordansjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600304</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6972313</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2025_0506</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karin Halldin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106670</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131106774</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nordansjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600324</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6972295</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2025_0402</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131106774</t>
         </is>
@@ -3762,6 +4107,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
